--- a/Impact factor and cost by region (using means).xlsx
+++ b/Impact factor and cost by region (using means).xlsx
@@ -73,7 +73,7 @@
     <t xml:space="preserve">5.1 (range: 0.0 to 88.5)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52 (range: 0.01 to 93.00)</t>
+    <t xml:space="preserve">1.04 (range: 0.01 to 23.28)</t>
   </si>
   <si>
     <t xml:space="preserve">9,882 (range: 20 to 347,563)</t>
@@ -121,7 +121,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">7.0 (range: 0.2 to 232.4)</t>
+    <t xml:space="preserve">6.9 (range: 0.2 to 232.4)</t>
   </si>
   <si>
     <t xml:space="preserve">1.95 (range: 0.05 to 112.16)</t>
@@ -700,7 +700,7 @@
         <v>7</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G4" s="9" t="n">
         <v>4</v>
